--- a/reports/Debug-snowbowl-20260106/For Winter Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/For Winter Ending (Actual)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Uplift Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Tickets</t>
   </si>
   <si>
     <t>Snowbowl Comp Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45969</v>
+        <v>45982</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45969</v>
+        <v>45982</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>45983</v>
       </c>
       <c r="C5" s="2">
-        <v>947</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45984</v>
+        <v>45983</v>
       </c>
       <c r="C6" s="2">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45986</v>
+        <v>45983</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,10 +515,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45986</v>
+        <v>45984</v>
       </c>
       <c r="C8" s="2">
-        <v>1210</v>
+        <v>288</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45987</v>
+        <v>45985</v>
       </c>
       <c r="C9" s="2">
-        <v>284</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="C10" s="2">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="C11" s="2">
-        <v>1400</v>
+        <v>1280</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45990</v>
+        <v>45987</v>
       </c>
       <c r="C12" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -585,13 +585,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45990</v>
+        <v>45987</v>
       </c>
       <c r="C13" s="2">
+        <v>240</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45990</v>
+        <v>45988</v>
       </c>
       <c r="C14" s="2">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>672</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45993</v>
+        <v>45990</v>
       </c>
       <c r="C16" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -641,13 +641,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45993</v>
+        <v>45990</v>
       </c>
       <c r="C17" s="2">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="C18" s="2">
-        <v>33</v>
+        <v>964</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45995</v>
+        <v>45993</v>
       </c>
       <c r="C19" s="2">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45997</v>
+        <v>45994</v>
       </c>
       <c r="C20" s="2">
-        <v>235</v>
+        <v>593</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,10 +697,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -711,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="C22" s="2">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="C23" s="2">
-        <v>1151</v>
+        <v>1090</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>45999</v>
       </c>
       <c r="C24" s="2">
-        <v>2</v>
+        <v>1056</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>46000</v>
       </c>
       <c r="C25" s="2">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C26" s="2">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C27" s="2">
-        <v>97</v>
+        <v>1080</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C28" s="2">
-        <v>725</v>
+        <v>133</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,10 +809,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C29" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -823,13 +823,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C30" s="2">
-        <v>68</v>
+        <v>1546</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="C31" s="2">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="C32" s="2">
-        <v>847</v>
+        <v>129</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,10 +865,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46005</v>
+        <v>46008</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -879,10 +879,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C34" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -893,13 +893,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C35" s="2">
-        <v>574</v>
+        <v>170</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46009</v>
+        <v>46011</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="C38" s="2">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>46012</v>
       </c>
       <c r="C39" s="2">
-        <v>1780</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46015</v>
+        <v>46012</v>
       </c>
       <c r="C40" s="2">
-        <v>1553</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,13 +977,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46016</v>
+        <v>46013</v>
       </c>
       <c r="C41" s="2">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,10 +991,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1005,13 +1005,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C43" s="2">
-        <v>1261</v>
+        <v>809</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46019</v>
+        <v>46015</v>
       </c>
       <c r="C44" s="2">
-        <v>333</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46021</v>
+        <v>46016</v>
       </c>
       <c r="C45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46021</v>
+        <v>46016</v>
       </c>
       <c r="C46" s="2">
-        <v>1704</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>6</v>
@@ -1061,10 +1061,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46022</v>
+        <v>46016</v>
       </c>
       <c r="C47" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1075,13 +1075,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46022</v>
+        <v>46017</v>
       </c>
       <c r="C48" s="2">
-        <v>421</v>
+        <v>22</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46023</v>
+        <v>46017</v>
       </c>
       <c r="C49" s="2">
-        <v>374</v>
+        <v>623</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46024</v>
+        <v>46019</v>
       </c>
       <c r="C50" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46024</v>
+        <v>46020</v>
       </c>
       <c r="C51" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1131,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C52" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C53" s="2">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46027</v>
+        <v>46022</v>
       </c>
       <c r="C54" s="2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1173,10 +1173,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45965</v>
+        <v>46023</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>652</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1187,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45969</v>
+        <v>46025</v>
       </c>
       <c r="C56" s="2">
-        <v>434</v>
+        <v>19</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45980</v>
+        <v>46025</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>1917</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1215,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45982</v>
+        <v>46025</v>
       </c>
       <c r="C58" s="2">
-        <v>1451</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1229,13 +1229,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45982</v>
+        <v>46028</v>
       </c>
       <c r="C59" s="2">
-        <v>567</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,13 +1243,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45983</v>
+        <v>46028</v>
       </c>
       <c r="C60" s="2">
-        <v>1</v>
+        <v>1546</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1257,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45983</v>
+        <v>45981</v>
       </c>
       <c r="C61" s="2">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1285,13 +1285,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45985</v>
+        <v>45983</v>
       </c>
       <c r="C63" s="2">
-        <v>1220</v>
+        <v>18</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1299,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45986</v>
+        <v>45984</v>
       </c>
       <c r="C64" s="2">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1313,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="C65" s="2">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>45986</v>
       </c>
       <c r="C66" s="2">
-        <v>201</v>
+        <v>24</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>45988</v>
       </c>
       <c r="C67" s="2">
-        <v>5</v>
+        <v>556</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>45989</v>
       </c>
       <c r="C68" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1372,7 +1372,7 @@
         <v>45989</v>
       </c>
       <c r="C69" s="2">
-        <v>5</v>
+        <v>1141</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1383,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="C70" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C71" s="2">
-        <v>281</v>
+        <v>362</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C72" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1425,10 +1425,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C73" s="2">
-        <v>15</v>
+        <v>656</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1439,13 +1439,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C74" s="2">
-        <v>2</v>
+        <v>796</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1453,10 +1453,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45991</v>
+        <v>45995</v>
       </c>
       <c r="C75" s="2">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="C76" s="2">
-        <v>7</v>
+        <v>803</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1481,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>860</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1495,13 +1495,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="C78" s="2">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45994</v>
+        <v>45997</v>
       </c>
       <c r="C79" s="2">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1523,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45995</v>
+        <v>45998</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -1537,13 +1537,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>1393</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1551,13 +1551,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="C82" s="2">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,13 +1565,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45998</v>
+        <v>46001</v>
       </c>
       <c r="C83" s="2">
-        <v>205</v>
+        <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C84" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C85" s="2">
-        <v>79</v>
+        <v>1002</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1607,13 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C86" s="2">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>46002</v>
       </c>
       <c r="C87" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>46002</v>
       </c>
       <c r="C88" s="2">
-        <v>741</v>
+        <v>91</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>46003</v>
       </c>
       <c r="C89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>5</v>
@@ -1666,10 +1666,10 @@
         <v>46004</v>
       </c>
       <c r="C90" s="2">
-        <v>417</v>
+        <v>5</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>46005</v>
       </c>
       <c r="C91" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1694,7 +1694,7 @@
         <v>46005</v>
       </c>
       <c r="C92" s="2">
-        <v>993</v>
+        <v>2</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
@@ -1705,13 +1705,13 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>46007</v>
+        <v>46005</v>
       </c>
       <c r="C93" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>46007</v>
+        <v>46005</v>
       </c>
       <c r="C94" s="2">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1733,10 +1733,10 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C95" s="2">
-        <v>596</v>
+        <v>6</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1747,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C96" s="2">
-        <v>1497</v>
+        <v>90</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="C97" s="2">
         <v>2</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>46011</v>
+        <v>46008</v>
       </c>
       <c r="C98" s="2">
         <v>2</v>
@@ -1789,10 +1789,10 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>46011</v>
+        <v>46010</v>
       </c>
       <c r="C99" s="2">
-        <v>794</v>
+        <v>109</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,10 +1806,10 @@
         <v>46011</v>
       </c>
       <c r="C100" s="2">
-        <v>1775</v>
+        <v>21</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1817,13 +1817,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="C101" s="2">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1831,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>46014</v>
+        <v>46011</v>
       </c>
       <c r="C102" s="2">
-        <v>4</v>
+        <v>350</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,13 +1845,13 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>46014</v>
+        <v>46012</v>
       </c>
       <c r="C103" s="2">
-        <v>1873</v>
+        <v>18</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1859,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>46015</v>
+        <v>46013</v>
       </c>
       <c r="C104" s="2">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,13 +1873,13 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="C106" s="2">
-        <v>305</v>
+        <v>693</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,10 +1901,10 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="C107" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1915,10 +1915,10 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="C108" s="2">
-        <v>5</v>
+        <v>392</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1929,10 +1929,10 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="C109" s="2">
-        <v>931</v>
+        <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>6</v>
@@ -1943,13 +1943,13 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>46018</v>
+        <v>46021</v>
       </c>
       <c r="C110" s="2">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C111" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1971,10 +1971,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C112" s="2">
-        <v>48</v>
+        <v>460</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1985,10 +1985,10 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>46021</v>
+        <v>46023</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -1999,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C114" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2013,10 +2013,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C115" s="2">
-        <v>39</v>
+        <v>987</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2030,10 +2030,10 @@
         <v>46024</v>
       </c>
       <c r="C116" s="2">
-        <v>13</v>
+        <v>1622</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C117" s="2">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2055,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C118" s="2">
-        <v>378</v>
+        <v>2</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2069,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C119" s="2">
-        <v>3</v>
+        <v>452</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,10 +2083,10 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="C120" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
@@ -2111,10 +2111,10 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="C122" s="2">
-        <v>44</v>
+        <v>550</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>45983</v>
+        <v>46027</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>1826</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>45983</v>
+        <v>46028</v>
       </c>
       <c r="C124" s="2">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2153,7 +2153,7 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>45983</v>
+        <v>45965</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>45984</v>
+        <v>45969</v>
       </c>
       <c r="C126" s="2">
-        <v>288</v>
+        <v>434</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>45985</v>
+        <v>45980</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C128" s="2">
-        <v>52</v>
+        <v>1451</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>5</v>
@@ -2209,13 +2209,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="C129" s="2">
-        <v>1280</v>
+        <v>567</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2223,10 +2223,10 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>45987</v>
+        <v>45983</v>
       </c>
       <c r="C130" s="2">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2237,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>45987</v>
+        <v>45983</v>
       </c>
       <c r="C131" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>8</v>
@@ -2251,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C132" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>5</v>
@@ -2265,13 +2265,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C133" s="2">
-        <v>672</v>
+        <v>1220</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,10 +2279,10 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>45990</v>
+        <v>45986</v>
       </c>
       <c r="C134" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>45990</v>
+        <v>45986</v>
       </c>
       <c r="C135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -2307,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>45991</v>
+        <v>45986</v>
       </c>
       <c r="C136" s="2">
-        <v>964</v>
+        <v>201</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2321,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>45993</v>
+        <v>45988</v>
       </c>
       <c r="C137" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2335,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>45994</v>
+        <v>45989</v>
       </c>
       <c r="C138" s="2">
-        <v>593</v>
+        <v>11</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,10 +2349,10 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="C139" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2363,10 +2363,10 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="C140" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2377,13 +2377,13 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="C141" s="2">
-        <v>1090</v>
+        <v>281</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2391,13 +2391,13 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>45999</v>
+        <v>45990</v>
       </c>
       <c r="C142" s="2">
-        <v>1057</v>
+        <v>1</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,13 +2405,13 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>46000</v>
+        <v>45991</v>
       </c>
       <c r="C143" s="2">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2419,10 +2419,10 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>46002</v>
+        <v>45991</v>
       </c>
       <c r="C144" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>46002</v>
+        <v>45991</v>
       </c>
       <c r="C145" s="2">
-        <v>1080</v>
+        <v>54</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2447,13 +2447,13 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>46003</v>
+        <v>45992</v>
       </c>
       <c r="C146" s="2">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>46005</v>
+        <v>45992</v>
       </c>
       <c r="C147" s="2">
         <v>1</v>
@@ -2475,13 +2475,13 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>46005</v>
+        <v>45994</v>
       </c>
       <c r="C148" s="2">
-        <v>1546</v>
+        <v>2</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2489,10 +2489,10 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>46006</v>
+        <v>45994</v>
       </c>
       <c r="C149" s="2">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2503,13 +2503,13 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>46006</v>
+        <v>45995</v>
       </c>
       <c r="C150" s="2">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2517,10 +2517,10 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>46008</v>
+        <v>45996</v>
       </c>
       <c r="C151" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>5</v>
@@ -2531,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>46009</v>
+        <v>45997</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2545,13 +2545,13 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>46009</v>
+        <v>45998</v>
       </c>
       <c r="C153" s="2">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2559,13 +2559,13 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="C154" s="2">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,10 +2573,10 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>46011</v>
+        <v>46000</v>
       </c>
       <c r="C155" s="2">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2587,13 +2587,13 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>46011</v>
+        <v>46001</v>
       </c>
       <c r="C156" s="2">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2601,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>46012</v>
+        <v>46002</v>
       </c>
       <c r="C157" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2615,10 +2615,10 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>46012</v>
+        <v>46002</v>
       </c>
       <c r="C158" s="2">
-        <v>2</v>
+        <v>741</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>5</v>
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C159" s="2">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2643,13 +2643,13 @@
         <v>1</v>
       </c>
       <c r="B160" s="2">
-        <v>46014</v>
+        <v>46004</v>
       </c>
       <c r="C160" s="2">
-        <v>51</v>
+        <v>417</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2657,10 +2657,10 @@
         <v>1</v>
       </c>
       <c r="B161" s="2">
-        <v>46014</v>
+        <v>46005</v>
       </c>
       <c r="C161" s="2">
-        <v>809</v>
+        <v>12</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>5</v>
@@ -2671,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="B162" s="2">
-        <v>46015</v>
+        <v>46005</v>
       </c>
       <c r="C162" s="2">
-        <v>2</v>
+        <v>993</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2685,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>46016</v>
+        <v>46007</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2699,13 +2699,13 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>46016</v>
+        <v>46007</v>
       </c>
       <c r="C164" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2713,10 +2713,10 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>46016</v>
+        <v>46008</v>
       </c>
       <c r="C165" s="2">
-        <v>1</v>
+        <v>596</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2727,13 +2727,13 @@
         <v>1</v>
       </c>
       <c r="B166" s="2">
-        <v>46017</v>
+        <v>46008</v>
       </c>
       <c r="C166" s="2">
-        <v>22</v>
+        <v>1497</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2741,10 +2741,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>46017</v>
+        <v>46009</v>
       </c>
       <c r="C167" s="2">
-        <v>623</v>
+        <v>2</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2755,10 +2755,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>46019</v>
+        <v>46011</v>
       </c>
       <c r="C168" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2769,10 +2769,10 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>46020</v>
+        <v>46011</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>794</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2783,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>46020</v>
+        <v>46011</v>
       </c>
       <c r="C170" s="2">
-        <v>2</v>
+        <v>1775</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2797,13 +2797,13 @@
         <v>1</v>
       </c>
       <c r="B171" s="2">
-        <v>46020</v>
+        <v>46012</v>
       </c>
       <c r="C171" s="2">
-        <v>511</v>
+        <v>339</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2811,10 +2811,10 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>46022</v>
+        <v>46014</v>
       </c>
       <c r="C172" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>5</v>
@@ -2825,13 +2825,13 @@
         <v>1</v>
       </c>
       <c r="B173" s="2">
-        <v>46023</v>
+        <v>46014</v>
       </c>
       <c r="C173" s="2">
-        <v>652</v>
+        <v>1873</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2839,10 +2839,10 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>46025</v>
+        <v>46015</v>
       </c>
       <c r="C174" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2853,13 +2853,13 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>46025</v>
+        <v>46015</v>
       </c>
       <c r="C175" s="2">
-        <v>1917</v>
+        <v>2</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2867,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>46025</v>
+        <v>46015</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2881,10 +2881,10 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>46028</v>
+        <v>46017</v>
       </c>
       <c r="C177" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2895,13 +2895,13 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>46028</v>
+        <v>46017</v>
       </c>
       <c r="C178" s="2">
-        <v>1546</v>
+        <v>5</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="2">
-        <v>45981</v>
+        <v>46017</v>
       </c>
       <c r="C179" s="2">
-        <v>27</v>
+        <v>931</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2923,13 +2923,13 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>45982</v>
+        <v>46018</v>
       </c>
       <c r="C180" s="2">
-        <v>15</v>
+        <v>234</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>45983</v>
+        <v>46020</v>
       </c>
       <c r="C181" s="2">
-        <v>1204</v>
+        <v>2</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>5</v>
@@ -2951,10 +2951,10 @@
         <v>1</v>
       </c>
       <c r="B182" s="2">
-        <v>45984</v>
+        <v>46020</v>
       </c>
       <c r="C182" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2965,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>45985</v>
+        <v>46021</v>
       </c>
       <c r="C183" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2979,10 +2979,10 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>45985</v>
+        <v>46023</v>
       </c>
       <c r="C184" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>5</v>
@@ -2993,10 +2993,10 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>45986</v>
+        <v>46023</v>
       </c>
       <c r="C185" s="2">
-        <v>999</v>
+        <v>39</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>5</v>
@@ -3007,10 +3007,10 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>45987</v>
+        <v>46024</v>
       </c>
       <c r="C186" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>5</v>
@@ -3021,10 +3021,10 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>45988</v>
+        <v>46026</v>
       </c>
       <c r="C187" s="2">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3035,13 +3035,13 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>45990</v>
+        <v>46027</v>
       </c>
       <c r="C188" s="2">
-        <v>2</v>
+        <v>378</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3049,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>45990</v>
+        <v>46028</v>
       </c>
       <c r="C189" s="2">
         <v>3</v>
@@ -3063,10 +3063,10 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>45991</v>
+        <v>45969</v>
       </c>
       <c r="C190" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3077,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>45992</v>
+        <v>45969</v>
       </c>
       <c r="C191" s="2">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3091,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>45994</v>
+        <v>45975</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3105,10 +3105,10 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>45995</v>
+        <v>45983</v>
       </c>
       <c r="C193" s="2">
-        <v>78</v>
+        <v>947</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>7</v>
@@ -3119,13 +3119,13 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>45998</v>
+        <v>45984</v>
       </c>
       <c r="C194" s="2">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,13 +3133,13 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>45998</v>
+        <v>45986</v>
       </c>
       <c r="C195" s="2">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3147,13 +3147,13 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>46000</v>
+        <v>45986</v>
       </c>
       <c r="C196" s="2">
-        <v>2</v>
+        <v>1210</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3161,13 +3161,13 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>46001</v>
+        <v>45987</v>
       </c>
       <c r="C197" s="2">
-        <v>9</v>
+        <v>284</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3175,13 +3175,13 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>46001</v>
+        <v>45989</v>
       </c>
       <c r="C198" s="2">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3189,13 +3189,13 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>46002</v>
+        <v>45989</v>
       </c>
       <c r="C199" s="2">
-        <v>82</v>
+        <v>1400</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3203,10 +3203,10 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>46003</v>
+        <v>45990</v>
       </c>
       <c r="C200" s="2">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>5</v>
@@ -3217,10 +3217,10 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>46004</v>
+        <v>45990</v>
       </c>
       <c r="C201" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3231,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>46004</v>
+        <v>45990</v>
       </c>
       <c r="C202" s="2">
-        <v>1583</v>
+        <v>239</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3245,13 +3245,13 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>46005</v>
+        <v>45992</v>
       </c>
       <c r="C203" s="2">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3259,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>46006</v>
+        <v>45993</v>
       </c>
       <c r="C204" s="2">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>46006</v>
+        <v>45993</v>
       </c>
       <c r="C205" s="2">
-        <v>661</v>
+        <v>67</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3287,10 +3287,10 @@
         <v>1</v>
       </c>
       <c r="B206" s="2">
-        <v>46007</v>
+        <v>45994</v>
       </c>
       <c r="C206" s="2">
-        <v>1410</v>
+        <v>33</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>6</v>
@@ -3301,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>46008</v>
+        <v>45995</v>
       </c>
       <c r="C207" s="2">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>5</v>
@@ -3315,13 +3315,13 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>46008</v>
+        <v>45997</v>
       </c>
       <c r="C208" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3329,10 +3329,10 @@
         <v>1</v>
       </c>
       <c r="B209" s="2">
-        <v>46009</v>
+        <v>45997</v>
       </c>
       <c r="C209" s="2">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>5</v>
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>46009</v>
+        <v>45998</v>
       </c>
       <c r="C210" s="2">
-        <v>592</v>
+        <v>93</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>5</v>
@@ -3357,10 +3357,10 @@
         <v>1</v>
       </c>
       <c r="B211" s="2">
-        <v>46010</v>
+        <v>45998</v>
       </c>
       <c r="C211" s="2">
-        <v>5</v>
+        <v>1151</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>5</v>
@@ -3371,10 +3371,10 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="C212" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>5</v>
@@ -3385,13 +3385,13 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="C213" s="2">
-        <v>1338</v>
+        <v>7</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,13 +3399,13 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>46011</v>
+        <v>46000</v>
       </c>
       <c r="C214" s="2">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3413,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>46012</v>
+        <v>46001</v>
       </c>
       <c r="C215" s="2">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3427,10 +3427,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="2">
-        <v>46012</v>
+        <v>46001</v>
       </c>
       <c r="C216" s="2">
-        <v>833</v>
+        <v>725</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>5</v>
@@ -3441,10 +3441,10 @@
         <v>1</v>
       </c>
       <c r="B217" s="2">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C217" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3455,13 +3455,13 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C218" s="2">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3469,13 +3469,13 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>46013</v>
+        <v>46004</v>
       </c>
       <c r="C219" s="2">
-        <v>2065</v>
+        <v>70</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3483,10 +3483,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>46014</v>
+        <v>46004</v>
       </c>
       <c r="C220" s="2">
-        <v>6</v>
+        <v>847</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3497,10 +3497,10 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>46015</v>
+        <v>46005</v>
       </c>
       <c r="C221" s="2">
-        <v>363</v>
+        <v>1</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>5</v>
@@ -3511,10 +3511,10 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="C222" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>5</v>
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="2">
-        <v>46017</v>
+        <v>46007</v>
       </c>
       <c r="C223" s="2">
-        <v>7</v>
+        <v>574</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3539,10 +3539,10 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>46017</v>
+        <v>46008</v>
       </c>
       <c r="C224" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>5</v>
@@ -3553,10 +3553,10 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>46019</v>
+        <v>46009</v>
       </c>
       <c r="C225" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3567,13 +3567,13 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>46021</v>
+        <v>46012</v>
       </c>
       <c r="C226" s="2">
-        <v>601</v>
+        <v>4</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3581,10 +3581,10 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>46024</v>
+        <v>46012</v>
       </c>
       <c r="C227" s="2">
-        <v>631</v>
+        <v>1780</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>7</v>
@@ -3595,13 +3595,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>46027</v>
+        <v>46015</v>
       </c>
       <c r="C228" s="2">
-        <v>1</v>
+        <v>1553</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3609,13 +3609,13 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>46027</v>
+        <v>46016</v>
       </c>
       <c r="C229" s="2">
-        <v>368</v>
+        <v>202</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3623,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>46027</v>
+        <v>46018</v>
       </c>
       <c r="C230" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>5</v>
@@ -3637,13 +3637,13 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>45971</v>
+        <v>46018</v>
       </c>
       <c r="C231" s="2">
-        <v>3</v>
+        <v>1261</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,13 +3651,13 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>45975</v>
+        <v>46019</v>
       </c>
       <c r="C232" s="2">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3665,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>45981</v>
+        <v>46021</v>
       </c>
       <c r="C233" s="2">
-        <v>265</v>
+        <v>3</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3679,13 +3679,13 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>45983</v>
+        <v>46021</v>
       </c>
       <c r="C234" s="2">
-        <v>1</v>
+        <v>1704</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3693,13 +3693,13 @@
         <v>1</v>
       </c>
       <c r="B235" s="2">
-        <v>45983</v>
+        <v>46022</v>
       </c>
       <c r="C235" s="2">
-        <v>243</v>
+        <v>3</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3707,13 +3707,13 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>45984</v>
+        <v>46022</v>
       </c>
       <c r="C236" s="2">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3721,13 +3721,13 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>45984</v>
+        <v>46023</v>
       </c>
       <c r="C237" s="2">
-        <v>3</v>
+        <v>374</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3735,10 +3735,10 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>45984</v>
+        <v>46024</v>
       </c>
       <c r="C238" s="2">
-        <v>1514</v>
+        <v>14</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>5</v>
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>45986</v>
+        <v>46024</v>
       </c>
       <c r="C239" s="2">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3763,10 +3763,10 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>45987</v>
+        <v>46025</v>
       </c>
       <c r="C240" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>5</v>
@@ -3777,13 +3777,13 @@
         <v>1</v>
       </c>
       <c r="B241" s="2">
-        <v>45987</v>
+        <v>46026</v>
       </c>
       <c r="C241" s="2">
-        <v>1034</v>
+        <v>539</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3791,13 +3791,13 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>45988</v>
+        <v>46027</v>
       </c>
       <c r="C242" s="2">
-        <v>239</v>
+        <v>32</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3805,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>45990</v>
+        <v>45971</v>
       </c>
       <c r="C243" s="2">
-        <v>962</v>
+        <v>3</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3819,13 +3819,13 @@
         <v>1</v>
       </c>
       <c r="B244" s="2">
-        <v>45991</v>
+        <v>45975</v>
       </c>
       <c r="C244" s="2">
-        <v>197</v>
+        <v>1</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3833,10 +3833,10 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="C245" s="2">
-        <v>2</v>
+        <v>265</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>5</v>
@@ -3847,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="B246" s="2">
-        <v>45994</v>
+        <v>45983</v>
       </c>
       <c r="C246" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>5</v>
@@ -3861,13 +3861,13 @@
         <v>1</v>
       </c>
       <c r="B247" s="2">
-        <v>45994</v>
+        <v>45983</v>
       </c>
       <c r="C247" s="2">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3875,10 +3875,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="2">
-        <v>45997</v>
+        <v>45984</v>
       </c>
       <c r="C248" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>5</v>
@@ -3889,13 +3889,13 @@
         <v>1</v>
       </c>
       <c r="B249" s="2">
-        <v>45997</v>
+        <v>45984</v>
       </c>
       <c r="C249" s="2">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3903,10 +3903,10 @@
         <v>1</v>
       </c>
       <c r="B250" s="2">
-        <v>45999</v>
+        <v>45984</v>
       </c>
       <c r="C250" s="2">
-        <v>66</v>
+        <v>1514</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>5</v>
@@ -3917,10 +3917,10 @@
         <v>1</v>
       </c>
       <c r="B251" s="2">
-        <v>46000</v>
+        <v>45986</v>
       </c>
       <c r="C251" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>5</v>
@@ -3931,13 +3931,13 @@
         <v>1</v>
       </c>
       <c r="B252" s="2">
-        <v>46000</v>
+        <v>45987</v>
       </c>
       <c r="C252" s="2">
-        <v>911</v>
+        <v>1</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3945,10 +3945,10 @@
         <v>1</v>
       </c>
       <c r="B253" s="2">
-        <v>46002</v>
+        <v>45987</v>
       </c>
       <c r="C253" s="2">
-        <v>79</v>
+        <v>1034</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>5</v>
@@ -3959,13 +3959,13 @@
         <v>1</v>
       </c>
       <c r="B254" s="2">
-        <v>46003</v>
+        <v>45988</v>
       </c>
       <c r="C254" s="2">
-        <v>1</v>
+        <v>239</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3973,13 +3973,13 @@
         <v>1</v>
       </c>
       <c r="B255" s="2">
-        <v>46003</v>
+        <v>45990</v>
       </c>
       <c r="C255" s="2">
-        <v>1103</v>
+        <v>962</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3987,13 +3987,13 @@
         <v>1</v>
       </c>
       <c r="B256" s="2">
-        <v>46004</v>
+        <v>45991</v>
       </c>
       <c r="C256" s="2">
-        <v>2</v>
+        <v>197</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4001,10 +4001,10 @@
         <v>1</v>
       </c>
       <c r="B257" s="2">
-        <v>46004</v>
+        <v>45992</v>
       </c>
       <c r="C257" s="2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>5</v>
@@ -4015,10 +4015,10 @@
         <v>1</v>
       </c>
       <c r="B258" s="2">
-        <v>46005</v>
+        <v>45994</v>
       </c>
       <c r="C258" s="2">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>5</v>
@@ -4029,13 +4029,13 @@
         <v>1</v>
       </c>
       <c r="B259" s="2">
-        <v>46006</v>
+        <v>45994</v>
       </c>
       <c r="C259" s="2">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4043,13 +4043,13 @@
         <v>1</v>
       </c>
       <c r="B260" s="2">
-        <v>46006</v>
+        <v>45997</v>
       </c>
       <c r="C260" s="2">
-        <v>1389</v>
+        <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4057,10 +4057,10 @@
         <v>1</v>
       </c>
       <c r="B261" s="2">
-        <v>46006</v>
+        <v>45997</v>
       </c>
       <c r="C261" s="2">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>8</v>
@@ -4071,10 +4071,10 @@
         <v>1</v>
       </c>
       <c r="B262" s="2">
-        <v>46007</v>
+        <v>45999</v>
       </c>
       <c r="C262" s="2">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>5</v>
@@ -4085,10 +4085,10 @@
         <v>1</v>
       </c>
       <c r="B263" s="2">
-        <v>46008</v>
+        <v>46000</v>
       </c>
       <c r="C263" s="2">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>5</v>
@@ -4099,13 +4099,13 @@
         <v>1</v>
       </c>
       <c r="B264" s="2">
-        <v>46009</v>
+        <v>46000</v>
       </c>
       <c r="C264" s="2">
-        <v>10</v>
+        <v>911</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4113,13 +4113,13 @@
         <v>1</v>
       </c>
       <c r="B265" s="2">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C265" s="2">
-        <v>1440</v>
+        <v>79</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4127,13 +4127,13 @@
         <v>1</v>
       </c>
       <c r="B266" s="2">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c r="C266" s="2">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4141,13 +4141,13 @@
         <v>1</v>
       </c>
       <c r="B267" s="2">
-        <v>46010</v>
+        <v>46003</v>
       </c>
       <c r="C267" s="2">
-        <v>10</v>
+        <v>1102</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4155,10 +4155,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="2">
-        <v>46010</v>
+        <v>46004</v>
       </c>
       <c r="C268" s="2">
-        <v>1017</v>
+        <v>2</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>5</v>
@@ -4169,10 +4169,10 @@
         <v>1</v>
       </c>
       <c r="B269" s="2">
-        <v>46012</v>
+        <v>46004</v>
       </c>
       <c r="C269" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>5</v>
@@ -4183,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="B270" s="2">
-        <v>46012</v>
+        <v>46005</v>
       </c>
       <c r="C270" s="2">
-        <v>321</v>
+        <v>91</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4197,10 +4197,10 @@
         <v>1</v>
       </c>
       <c r="B271" s="2">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C271" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>5</v>
@@ -4211,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="B272" s="2">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C272" s="2">
-        <v>1052</v>
+        <v>1389</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4225,13 +4225,13 @@
         <v>1</v>
       </c>
       <c r="B273" s="2">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="C273" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="B274" s="2">
-        <v>46016</v>
+        <v>46007</v>
       </c>
       <c r="C274" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>5</v>
@@ -4253,10 +4253,10 @@
         <v>1</v>
       </c>
       <c r="B275" s="2">
-        <v>46016</v>
+        <v>46008</v>
       </c>
       <c r="C275" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>5</v>
@@ -4267,13 +4267,13 @@
         <v>1</v>
       </c>
       <c r="B276" s="2">
-        <v>46017</v>
+        <v>46009</v>
       </c>
       <c r="C276" s="2">
-        <v>242</v>
+        <v>10</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4281,13 +4281,13 @@
         <v>1</v>
       </c>
       <c r="B277" s="2">
-        <v>46019</v>
+        <v>46009</v>
       </c>
       <c r="C277" s="2">
-        <v>479</v>
+        <v>1440</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4295,13 +4295,13 @@
         <v>1</v>
       </c>
       <c r="B278" s="2">
-        <v>46020</v>
+        <v>46009</v>
       </c>
       <c r="C278" s="2">
-        <v>578</v>
+        <v>118</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4309,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="B279" s="2">
-        <v>46023</v>
+        <v>46010</v>
       </c>
       <c r="C279" s="2">
         <v>10</v>
@@ -4323,10 +4323,10 @@
         <v>1</v>
       </c>
       <c r="B280" s="2">
-        <v>46023</v>
+        <v>46010</v>
       </c>
       <c r="C280" s="2">
-        <v>1</v>
+        <v>1017</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>5</v>
@@ -4337,13 +4337,13 @@
         <v>1</v>
       </c>
       <c r="B281" s="2">
-        <v>46023</v>
+        <v>46012</v>
       </c>
       <c r="C281" s="2">
-        <v>511</v>
+        <v>8</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4351,13 +4351,13 @@
         <v>1</v>
       </c>
       <c r="B282" s="2">
-        <v>46026</v>
+        <v>46012</v>
       </c>
       <c r="C282" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4365,10 +4365,10 @@
         <v>1</v>
       </c>
       <c r="B283" s="2">
-        <v>46028</v>
+        <v>46013</v>
       </c>
       <c r="C283" s="2">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>5</v>
@@ -4379,10 +4379,10 @@
         <v>1</v>
       </c>
       <c r="B284" s="2">
-        <v>45968</v>
+        <v>46013</v>
       </c>
       <c r="C284" s="2">
-        <v>1</v>
+        <v>1052</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>5</v>
@@ -4393,10 +4393,10 @@
         <v>1</v>
       </c>
       <c r="B285" s="2">
-        <v>45968</v>
+        <v>46015</v>
       </c>
       <c r="C285" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>5</v>
@@ -4407,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="B286" s="2">
-        <v>45981</v>
+        <v>46016</v>
       </c>
       <c r="C286" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>5</v>
@@ -4421,13 +4421,13 @@
         <v>1</v>
       </c>
       <c r="B287" s="2">
-        <v>45981</v>
+        <v>46016</v>
       </c>
       <c r="C287" s="2">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4435,13 +4435,13 @@
         <v>1</v>
       </c>
       <c r="B288" s="2">
-        <v>45983</v>
+        <v>46017</v>
       </c>
       <c r="C288" s="2">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4449,10 +4449,10 @@
         <v>1</v>
       </c>
       <c r="B289" s="2">
-        <v>45984</v>
+        <v>46019</v>
       </c>
       <c r="C289" s="2">
-        <v>5</v>
+        <v>479</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>5</v>
@@ -4463,13 +4463,13 @@
         <v>1</v>
       </c>
       <c r="B290" s="2">
-        <v>45984</v>
+        <v>46020</v>
       </c>
       <c r="C290" s="2">
-        <v>2</v>
+        <v>444</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4477,13 +4477,13 @@
         <v>1</v>
       </c>
       <c r="B291" s="2">
-        <v>45984</v>
+        <v>46023</v>
       </c>
       <c r="C291" s="2">
-        <v>943</v>
+        <v>10</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4491,10 +4491,10 @@
         <v>1</v>
       </c>
       <c r="B292" s="2">
-        <v>45986</v>
+        <v>46023</v>
       </c>
       <c r="C292" s="2">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>5</v>
@@ -4505,13 +4505,13 @@
         <v>1</v>
       </c>
       <c r="B293" s="2">
-        <v>45987</v>
+        <v>46023</v>
       </c>
       <c r="C293" s="2">
-        <v>3</v>
+        <v>439</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4519,13 +4519,13 @@
         <v>1</v>
       </c>
       <c r="B294" s="2">
-        <v>45987</v>
+        <v>46026</v>
       </c>
       <c r="C294" s="2">
-        <v>1431</v>
+        <v>268</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4533,10 +4533,10 @@
         <v>1</v>
       </c>
       <c r="B295" s="2">
-        <v>45989</v>
+        <v>46028</v>
       </c>
       <c r="C295" s="2">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>5</v>
@@ -4547,13 +4547,13 @@
         <v>1</v>
       </c>
       <c r="B296" s="2">
-        <v>45990</v>
+        <v>45981</v>
       </c>
       <c r="C296" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4561,13 +4561,13 @@
         <v>1</v>
       </c>
       <c r="B297" s="2">
-        <v>45990</v>
+        <v>45982</v>
       </c>
       <c r="C297" s="2">
-        <v>1620</v>
+        <v>15</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4575,13 +4575,13 @@
         <v>1</v>
       </c>
       <c r="B298" s="2">
-        <v>45990</v>
+        <v>45983</v>
       </c>
       <c r="C298" s="2">
-        <v>364</v>
+        <v>1204</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="B299" s="2">
-        <v>45991</v>
+        <v>45984</v>
       </c>
       <c r="C299" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>5</v>
@@ -4603,10 +4603,10 @@
         <v>1</v>
       </c>
       <c r="B300" s="2">
-        <v>45992</v>
+        <v>45985</v>
       </c>
       <c r="C300" s="2">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>5</v>
@@ -4617,10 +4617,10 @@
         <v>1</v>
       </c>
       <c r="B301" s="2">
-        <v>45993</v>
+        <v>45985</v>
       </c>
       <c r="C301" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>5</v>
@@ -4631,13 +4631,13 @@
         <v>1</v>
       </c>
       <c r="B302" s="2">
-        <v>45993</v>
+        <v>45986</v>
       </c>
       <c r="C302" s="2">
-        <v>738</v>
+        <v>999</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4645,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="B303" s="2">
-        <v>45993</v>
+        <v>45987</v>
       </c>
       <c r="C303" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4659,10 +4659,10 @@
         <v>1</v>
       </c>
       <c r="B304" s="2">
-        <v>45994</v>
+        <v>45988</v>
       </c>
       <c r="C304" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>5</v>
@@ -4673,10 +4673,10 @@
         <v>1</v>
       </c>
       <c r="B305" s="2">
-        <v>45996</v>
+        <v>45990</v>
       </c>
       <c r="C305" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>5</v>
@@ -4687,13 +4687,13 @@
         <v>1</v>
       </c>
       <c r="B306" s="2">
-        <v>45996</v>
+        <v>45990</v>
       </c>
       <c r="C306" s="2">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4701,10 +4701,10 @@
         <v>1</v>
       </c>
       <c r="B307" s="2">
-        <v>45997</v>
+        <v>45991</v>
       </c>
       <c r="C307" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>5</v>
@@ -4715,13 +4715,13 @@
         <v>1</v>
       </c>
       <c r="B308" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C308" s="2">
-        <v>1192</v>
+        <v>100</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4729,10 +4729,10 @@
         <v>1</v>
       </c>
       <c r="B309" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C309" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>5</v>
@@ -4743,10 +4743,10 @@
         <v>1</v>
       </c>
       <c r="B310" s="2">
-        <v>45999</v>
+        <v>45995</v>
       </c>
       <c r="C310" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>8</v>
@@ -4757,10 +4757,10 @@
         <v>1</v>
       </c>
       <c r="B311" s="2">
-        <v>46000</v>
+        <v>45998</v>
       </c>
       <c r="C311" s="2">
-        <v>570</v>
+        <v>2</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>5</v>
@@ -4771,13 +4771,13 @@
         <v>1</v>
       </c>
       <c r="B312" s="2">
-        <v>46001</v>
+        <v>45998</v>
       </c>
       <c r="C312" s="2">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4785,10 +4785,10 @@
         <v>1</v>
       </c>
       <c r="B313" s="2">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="C313" s="2">
-        <v>997</v>
+        <v>2</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>5</v>
@@ -4799,13 +4799,13 @@
         <v>1</v>
       </c>
       <c r="B314" s="2">
-        <v>46004</v>
+        <v>46001</v>
       </c>
       <c r="C314" s="2">
-        <v>243</v>
+        <v>9</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4813,13 +4813,13 @@
         <v>1</v>
       </c>
       <c r="B315" s="2">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C315" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4827,13 +4827,13 @@
         <v>1</v>
       </c>
       <c r="B316" s="2">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C316" s="2">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4841,13 +4841,13 @@
         <v>1</v>
       </c>
       <c r="B317" s="2">
-        <v>46010</v>
+        <v>46003</v>
       </c>
       <c r="C317" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4855,10 +4855,10 @@
         <v>1</v>
       </c>
       <c r="B318" s="2">
-        <v>46011</v>
+        <v>46004</v>
       </c>
       <c r="C318" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>5</v>
@@ -4869,13 +4869,13 @@
         <v>1</v>
       </c>
       <c r="B319" s="2">
-        <v>46013</v>
+        <v>46004</v>
       </c>
       <c r="C319" s="2">
-        <v>21</v>
+        <v>1582</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4883,13 +4883,13 @@
         <v>1</v>
       </c>
       <c r="B320" s="2">
-        <v>46013</v>
+        <v>46005</v>
       </c>
       <c r="C320" s="2">
-        <v>499</v>
+        <v>339</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4897,10 +4897,10 @@
         <v>1</v>
       </c>
       <c r="B321" s="2">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="C321" s="2">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>5</v>
@@ -4911,10 +4911,10 @@
         <v>1</v>
       </c>
       <c r="B322" s="2">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="C322" s="2">
-        <v>4</v>
+        <v>661</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>5</v>
@@ -4925,13 +4925,13 @@
         <v>1</v>
       </c>
       <c r="B323" s="2">
-        <v>46016</v>
+        <v>46007</v>
       </c>
       <c r="C323" s="2">
-        <v>6</v>
+        <v>1410</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4939,10 +4939,10 @@
         <v>1</v>
       </c>
       <c r="B324" s="2">
-        <v>46016</v>
+        <v>46008</v>
       </c>
       <c r="C324" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>5</v>
@@ -4953,10 +4953,10 @@
         <v>1</v>
       </c>
       <c r="B325" s="2">
-        <v>46016</v>
+        <v>46008</v>
       </c>
       <c r="C325" s="2">
-        <v>1128</v>
+        <v>77</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>6</v>
@@ -4967,10 +4967,10 @@
         <v>1</v>
       </c>
       <c r="B326" s="2">
-        <v>46018</v>
+        <v>46009</v>
       </c>
       <c r="C326" s="2">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>5</v>
@@ -4981,13 +4981,13 @@
         <v>1</v>
       </c>
       <c r="B327" s="2">
-        <v>46019</v>
+        <v>46009</v>
       </c>
       <c r="C327" s="2">
-        <v>1243</v>
+        <v>592</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4995,13 +4995,13 @@
         <v>1</v>
       </c>
       <c r="B328" s="2">
-        <v>46019</v>
+        <v>46010</v>
       </c>
       <c r="C328" s="2">
-        <v>612</v>
+        <v>5</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5009,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="B329" s="2">
-        <v>46020</v>
+        <v>46010</v>
       </c>
       <c r="C329" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>5</v>
@@ -5023,13 +5023,13 @@
         <v>1</v>
       </c>
       <c r="B330" s="2">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C330" s="2">
-        <v>53</v>
+        <v>1338</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5037,10 +5037,10 @@
         <v>1</v>
       </c>
       <c r="B331" s="2">
-        <v>46021</v>
+        <v>46011</v>
       </c>
       <c r="C331" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>5</v>
@@ -5051,10 +5051,10 @@
         <v>1</v>
       </c>
       <c r="B332" s="2">
-        <v>46022</v>
+        <v>46012</v>
       </c>
       <c r="C332" s="2">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>5</v>
@@ -5065,13 +5065,13 @@
         <v>1</v>
       </c>
       <c r="B333" s="2">
-        <v>46022</v>
+        <v>46012</v>
       </c>
       <c r="C333" s="2">
-        <v>1290</v>
+        <v>833</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5079,13 +5079,13 @@
         <v>1</v>
       </c>
       <c r="B334" s="2">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C334" s="2">
-        <v>482</v>
+        <v>9</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5093,10 +5093,10 @@
         <v>1</v>
       </c>
       <c r="B335" s="2">
-        <v>46023</v>
+        <v>46013</v>
       </c>
       <c r="C335" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>5</v>
@@ -5107,13 +5107,13 @@
         <v>1</v>
       </c>
       <c r="B336" s="2">
-        <v>46025</v>
+        <v>46013</v>
       </c>
       <c r="C336" s="2">
-        <v>12</v>
+        <v>2065</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5121,10 +5121,10 @@
         <v>1</v>
       </c>
       <c r="B337" s="2">
-        <v>46025</v>
+        <v>46014</v>
       </c>
       <c r="C337" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>5</v>
@@ -5135,13 +5135,13 @@
         <v>1</v>
       </c>
       <c r="B338" s="2">
-        <v>46025</v>
+        <v>46015</v>
       </c>
       <c r="C338" s="2">
-        <v>551</v>
+        <v>363</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="B339" s="2">
-        <v>46026</v>
+        <v>46016</v>
       </c>
       <c r="C339" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>5</v>
@@ -5163,10 +5163,10 @@
         <v>1</v>
       </c>
       <c r="B340" s="2">
-        <v>46026</v>
+        <v>46017</v>
       </c>
       <c r="C340" s="2">
-        <v>658</v>
+        <v>7</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>5</v>
@@ -5177,10 +5177,10 @@
         <v>1</v>
       </c>
       <c r="B341" s="2">
-        <v>46028</v>
+        <v>46017</v>
       </c>
       <c r="C341" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>5</v>
@@ -5191,13 +5191,13 @@
         <v>1</v>
       </c>
       <c r="B342" s="2">
-        <v>46028</v>
+        <v>46019</v>
       </c>
       <c r="C342" s="2">
-        <v>241</v>
+        <v>2</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5205,13 +5205,13 @@
         <v>1</v>
       </c>
       <c r="B343" s="2">
-        <v>45968</v>
+        <v>46021</v>
       </c>
       <c r="C343" s="2">
-        <v>1</v>
+        <v>499</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5219,13 +5219,13 @@
         <v>1</v>
       </c>
       <c r="B344" s="2">
-        <v>45969</v>
+        <v>46024</v>
       </c>
       <c r="C344" s="2">
-        <v>4</v>
+        <v>488</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5233,10 +5233,10 @@
         <v>1</v>
       </c>
       <c r="B345" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="C345" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>5</v>
@@ -5247,13 +5247,13 @@
         <v>1</v>
       </c>
       <c r="B346" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="C346" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5261,10 +5261,10 @@
         <v>1</v>
       </c>
       <c r="B347" s="2">
-        <v>45985</v>
+        <v>46027</v>
       </c>
       <c r="C347" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>5</v>
@@ -5275,13 +5275,13 @@
         <v>1</v>
       </c>
       <c r="B348" s="2">
-        <v>45985</v>
+        <v>45968</v>
       </c>
       <c r="C348" s="2">
         <v>1</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5289,13 +5289,13 @@
         <v>1</v>
       </c>
       <c r="B349" s="2">
-        <v>45985</v>
+        <v>45969</v>
       </c>
       <c r="C349" s="2">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5303,13 +5303,13 @@
         <v>1</v>
       </c>
       <c r="B350" s="2">
-        <v>45986</v>
+        <v>45982</v>
       </c>
       <c r="C350" s="2">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5317,13 +5317,13 @@
         <v>1</v>
       </c>
       <c r="B351" s="2">
-        <v>45987</v>
+        <v>45982</v>
       </c>
       <c r="C351" s="2">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5331,10 +5331,10 @@
         <v>1</v>
       </c>
       <c r="B352" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C352" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>5</v>
@@ -5345,10 +5345,10 @@
         <v>1</v>
       </c>
       <c r="B353" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C353" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>5</v>
@@ -5359,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="B354" s="2">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="C354" s="2">
-        <v>1268</v>
+        <v>133</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5373,13 +5373,13 @@
         <v>1</v>
       </c>
       <c r="B355" s="2">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="C355" s="2">
-        <v>462</v>
+        <v>136</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5387,10 +5387,10 @@
         <v>1</v>
       </c>
       <c r="B356" s="2">
-        <v>45990</v>
+        <v>45987</v>
       </c>
       <c r="C356" s="2">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>5</v>
@@ -5401,10 +5401,10 @@
         <v>1</v>
       </c>
       <c r="B357" s="2">
-        <v>45990</v>
+        <v>45988</v>
       </c>
       <c r="C357" s="2">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>5</v>
@@ -5415,10 +5415,10 @@
         <v>1</v>
       </c>
       <c r="B358" s="2">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="C358" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>5</v>
@@ -5429,13 +5429,13 @@
         <v>1</v>
       </c>
       <c r="B359" s="2">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="C359" s="2">
-        <v>4</v>
+        <v>1268</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5443,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="B360" s="2">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="C360" s="2">
-        <v>1315</v>
+        <v>462</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>6</v>
@@ -5457,13 +5457,13 @@
         <v>1</v>
       </c>
       <c r="B361" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C361" s="2">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5471,10 +5471,10 @@
         <v>1</v>
       </c>
       <c r="B362" s="2">
-        <v>45993</v>
+        <v>45990</v>
       </c>
       <c r="C362" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>5</v>
@@ -5485,10 +5485,10 @@
         <v>1</v>
       </c>
       <c r="B363" s="2">
-        <v>45993</v>
+        <v>45991</v>
       </c>
       <c r="C363" s="2">
-        <v>488</v>
+        <v>17</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>5</v>
@@ -5499,10 +5499,10 @@
         <v>1</v>
       </c>
       <c r="B364" s="2">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="C364" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>5</v>
@@ -5513,13 +5513,13 @@
         <v>1</v>
       </c>
       <c r="B365" s="2">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="C365" s="2">
-        <v>710</v>
+        <v>1315</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5527,13 +5527,13 @@
         <v>1</v>
       </c>
       <c r="B366" s="2">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="C366" s="2">
-        <v>9</v>
+        <v>117</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5541,13 +5541,13 @@
         <v>1</v>
       </c>
       <c r="B367" s="2">
-        <v>45995</v>
+        <v>45993</v>
       </c>
       <c r="C367" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5555,10 +5555,10 @@
         <v>1</v>
       </c>
       <c r="B368" s="2">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="C368" s="2">
-        <v>94</v>
+        <v>488</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>5</v>
@@ -5569,10 +5569,10 @@
         <v>1</v>
       </c>
       <c r="B369" s="2">
-        <v>45996</v>
+        <v>45994</v>
       </c>
       <c r="C369" s="2">
-        <v>1326</v>
+        <v>3</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>5</v>
@@ -5583,13 +5583,13 @@
         <v>1</v>
       </c>
       <c r="B370" s="2">
-        <v>45997</v>
+        <v>45994</v>
       </c>
       <c r="C370" s="2">
-        <v>2</v>
+        <v>710</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5597,13 +5597,13 @@
         <v>1</v>
       </c>
       <c r="B371" s="2">
-        <v>45997</v>
+        <v>45995</v>
       </c>
       <c r="C371" s="2">
-        <v>1621</v>
+        <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5611,13 +5611,13 @@
         <v>1</v>
       </c>
       <c r="B372" s="2">
-        <v>45998</v>
+        <v>45995</v>
       </c>
       <c r="C372" s="2">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5625,10 +5625,10 @@
         <v>1</v>
       </c>
       <c r="B373" s="2">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="C373" s="2">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>5</v>
@@ -5639,10 +5639,10 @@
         <v>1</v>
       </c>
       <c r="B374" s="2">
-        <v>45999</v>
+        <v>45996</v>
       </c>
       <c r="C374" s="2">
-        <v>718</v>
+        <v>1326</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>5</v>
@@ -5653,10 +5653,10 @@
         <v>1</v>
       </c>
       <c r="B375" s="2">
-        <v>45999</v>
+        <v>45997</v>
       </c>
       <c r="C375" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>5</v>
@@ -5667,13 +5667,13 @@
         <v>1</v>
       </c>
       <c r="B376" s="2">
-        <v>46000</v>
+        <v>45997</v>
       </c>
       <c r="C376" s="2">
+        <v>1621</v>
+      </c>
+      <c r="D376" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D376" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5681,10 +5681,10 @@
         <v>1</v>
       </c>
       <c r="B377" s="2">
-        <v>46001</v>
+        <v>45998</v>
       </c>
       <c r="C377" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D377" s="2" t="s">
         <v>5</v>
@@ -5695,10 +5695,10 @@
         <v>1</v>
       </c>
       <c r="B378" s="2">
-        <v>46003</v>
+        <v>45998</v>
       </c>
       <c r="C378" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>5</v>
@@ -5709,13 +5709,13 @@
         <v>1</v>
       </c>
       <c r="B379" s="2">
-        <v>46008</v>
+        <v>45999</v>
       </c>
       <c r="C379" s="2">
-        <v>118</v>
+        <v>718</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5723,10 +5723,10 @@
         <v>1</v>
       </c>
       <c r="B380" s="2">
-        <v>46011</v>
+        <v>45999</v>
       </c>
       <c r="C380" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>5</v>
@@ -5737,13 +5737,13 @@
         <v>1</v>
       </c>
       <c r="B381" s="2">
-        <v>46011</v>
+        <v>46000</v>
       </c>
       <c r="C381" s="2">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5751,10 +5751,10 @@
         <v>1</v>
       </c>
       <c r="B382" s="2">
-        <v>46011</v>
+        <v>46001</v>
       </c>
       <c r="C382" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>5</v>
@@ -5765,10 +5765,10 @@
         <v>1</v>
       </c>
       <c r="B383" s="2">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="C383" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>5</v>
@@ -5779,13 +5779,13 @@
         <v>1</v>
       </c>
       <c r="B384" s="2">
-        <v>46014</v>
+        <v>46008</v>
       </c>
       <c r="C384" s="2">
-        <v>443</v>
+        <v>118</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5793,13 +5793,13 @@
         <v>1</v>
       </c>
       <c r="B385" s="2">
-        <v>46015</v>
+        <v>46011</v>
       </c>
       <c r="C385" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5807,13 +5807,13 @@
         <v>1</v>
       </c>
       <c r="B386" s="2">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="C386" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5821,10 +5821,10 @@
         <v>1</v>
       </c>
       <c r="B387" s="2">
-        <v>46017</v>
+        <v>46011</v>
       </c>
       <c r="C387" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>5</v>
@@ -5835,13 +5835,13 @@
         <v>1</v>
       </c>
       <c r="B388" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C388" s="2">
-        <v>658</v>
+        <v>15</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5849,13 +5849,13 @@
         <v>1</v>
       </c>
       <c r="B389" s="2">
-        <v>46019</v>
+        <v>46014</v>
       </c>
       <c r="C389" s="2">
-        <v>43</v>
+        <v>402</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5863,13 +5863,13 @@
         <v>1</v>
       </c>
       <c r="B390" s="2">
-        <v>46020</v>
+        <v>46015</v>
       </c>
       <c r="C390" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5877,13 +5877,13 @@
         <v>1</v>
       </c>
       <c r="B391" s="2">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="C391" s="2">
-        <v>1688</v>
+        <v>20</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5891,13 +5891,13 @@
         <v>1</v>
       </c>
       <c r="B392" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C392" s="2">
-        <v>451</v>
+        <v>5</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5905,13 +5905,13 @@
         <v>1</v>
       </c>
       <c r="B393" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C393" s="2">
-        <v>55</v>
+        <v>658</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5919,10 +5919,10 @@
         <v>1</v>
       </c>
       <c r="B394" s="2">
-        <v>46022</v>
+        <v>46019</v>
       </c>
       <c r="C394" s="2">
-        <v>392</v>
+        <v>43</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>5</v>
@@ -5933,10 +5933,10 @@
         <v>1</v>
       </c>
       <c r="B395" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C395" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>5</v>
@@ -5947,13 +5947,13 @@
         <v>1</v>
       </c>
       <c r="B396" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C396" s="2">
-        <v>1420</v>
+        <v>1688</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5961,13 +5961,13 @@
         <v>1</v>
       </c>
       <c r="B397" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C397" s="2">
-        <v>15</v>
+        <v>451</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5975,13 +5975,13 @@
         <v>1</v>
       </c>
       <c r="B398" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="C398" s="2">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5989,10 +5989,10 @@
         <v>1</v>
       </c>
       <c r="B399" s="2">
-        <v>46025</v>
+        <v>46022</v>
       </c>
       <c r="C399" s="2">
-        <v>52</v>
+        <v>392</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>5</v>
@@ -6003,10 +6003,10 @@
         <v>1</v>
       </c>
       <c r="B400" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C400" s="2">
-        <v>844</v>
+        <v>2</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>5</v>
@@ -6017,13 +6017,13 @@
         <v>1</v>
       </c>
       <c r="B401" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C401" s="2">
-        <v>1</v>
+        <v>1420</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6031,10 +6031,10 @@
         <v>1</v>
       </c>
       <c r="B402" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C402" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>5</v>
@@ -6045,10 +6045,10 @@
         <v>1</v>
       </c>
       <c r="B403" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C403" s="2">
-        <v>1451</v>
+        <v>1</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>6</v>
@@ -6059,10 +6059,10 @@
         <v>1</v>
       </c>
       <c r="B404" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C404" s="2">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="D404" s="2" t="s">
         <v>5</v>
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="B405" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C405" s="2">
-        <v>472</v>
+        <v>844</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>5</v>
@@ -6087,10 +6087,10 @@
         <v>1</v>
       </c>
       <c r="B406" s="2">
-        <v>45981</v>
+        <v>46026</v>
       </c>
       <c r="C406" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>5</v>
@@ -6101,13 +6101,13 @@
         <v>1</v>
       </c>
       <c r="B407" s="2">
-        <v>45982</v>
+        <v>46026</v>
       </c>
       <c r="C407" s="2">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6115,13 +6115,13 @@
         <v>1</v>
       </c>
       <c r="B408" s="2">
-        <v>45983</v>
+        <v>46026</v>
       </c>
       <c r="C408" s="2">
-        <v>18</v>
+        <v>1451</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6129,10 +6129,10 @@
         <v>1</v>
       </c>
       <c r="B409" s="2">
-        <v>45984</v>
+        <v>46027</v>
       </c>
       <c r="C409" s="2">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>5</v>
@@ -6143,13 +6143,13 @@
         <v>1</v>
       </c>
       <c r="B410" s="2">
-        <v>45985</v>
+        <v>46028</v>
       </c>
       <c r="C410" s="2">
-        <v>176</v>
+        <v>472</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6157,10 +6157,10 @@
         <v>1</v>
       </c>
       <c r="B411" s="2">
-        <v>45986</v>
+        <v>45968</v>
       </c>
       <c r="C411" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>5</v>
@@ -6171,13 +6171,13 @@
         <v>1</v>
       </c>
       <c r="B412" s="2">
-        <v>45988</v>
+        <v>45968</v>
       </c>
       <c r="C412" s="2">
-        <v>556</v>
+        <v>3</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6185,10 +6185,10 @@
         <v>1</v>
       </c>
       <c r="B413" s="2">
-        <v>45989</v>
+        <v>45981</v>
       </c>
       <c r="C413" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>5</v>
@@ -6199,13 +6199,13 @@
         <v>1</v>
       </c>
       <c r="B414" s="2">
-        <v>45989</v>
+        <v>45981</v>
       </c>
       <c r="C414" s="2">
-        <v>1141</v>
+        <v>17</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6213,10 +6213,10 @@
         <v>1</v>
       </c>
       <c r="B415" s="2">
-        <v>45990</v>
+        <v>45983</v>
       </c>
       <c r="C415" s="2">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>5</v>
@@ -6227,13 +6227,13 @@
         <v>1</v>
       </c>
       <c r="B416" s="2">
-        <v>45991</v>
+        <v>45984</v>
       </c>
       <c r="C416" s="2">
-        <v>362</v>
+        <v>5</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6241,10 +6241,10 @@
         <v>1</v>
       </c>
       <c r="B417" s="2">
-        <v>45992</v>
+        <v>45984</v>
       </c>
       <c r="C417" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>5</v>
@@ -6255,13 +6255,13 @@
         <v>1</v>
       </c>
       <c r="B418" s="2">
-        <v>45992</v>
+        <v>45984</v>
       </c>
       <c r="C418" s="2">
-        <v>656</v>
+        <v>943</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6269,13 +6269,13 @@
         <v>1</v>
       </c>
       <c r="B419" s="2">
-        <v>45992</v>
+        <v>45986</v>
       </c>
       <c r="C419" s="2">
-        <v>796</v>
+        <v>58</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6283,10 +6283,10 @@
         <v>1</v>
       </c>
       <c r="B420" s="2">
-        <v>45995</v>
+        <v>45987</v>
       </c>
       <c r="C420" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>5</v>
@@ -6297,13 +6297,13 @@
         <v>1</v>
       </c>
       <c r="B421" s="2">
-        <v>45995</v>
+        <v>45987</v>
       </c>
       <c r="C421" s="2">
-        <v>803</v>
+        <v>1431</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6311,13 +6311,13 @@
         <v>1</v>
       </c>
       <c r="B422" s="2">
-        <v>45995</v>
+        <v>45989</v>
       </c>
       <c r="C422" s="2">
-        <v>860</v>
+        <v>39</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6325,13 +6325,13 @@
         <v>1</v>
       </c>
       <c r="B423" s="2">
-        <v>45996</v>
+        <v>45990</v>
       </c>
       <c r="C423" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6339,13 +6339,13 @@
         <v>1</v>
       </c>
       <c r="B424" s="2">
-        <v>45997</v>
+        <v>45990</v>
       </c>
       <c r="C424" s="2">
-        <v>1</v>
+        <v>1620</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6353,13 +6353,13 @@
         <v>1</v>
       </c>
       <c r="B425" s="2">
-        <v>45998</v>
+        <v>45990</v>
       </c>
       <c r="C425" s="2">
-        <v>1</v>
+        <v>364</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6367,13 +6367,13 @@
         <v>1</v>
       </c>
       <c r="B426" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C426" s="2">
-        <v>1393</v>
+        <v>14</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6381,13 +6381,13 @@
         <v>1</v>
       </c>
       <c r="B427" s="2">
-        <v>45999</v>
+        <v>45992</v>
       </c>
       <c r="C427" s="2">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6395,10 +6395,10 @@
         <v>1</v>
       </c>
       <c r="B428" s="2">
-        <v>46001</v>
+        <v>45993</v>
       </c>
       <c r="C428" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>5</v>
@@ -6409,13 +6409,13 @@
         <v>1</v>
       </c>
       <c r="B429" s="2">
-        <v>46001</v>
+        <v>45993</v>
       </c>
       <c r="C429" s="2">
-        <v>1</v>
+        <v>738</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6423,10 +6423,10 @@
         <v>1</v>
       </c>
       <c r="B430" s="2">
-        <v>46001</v>
+        <v>45993</v>
       </c>
       <c r="C430" s="2">
-        <v>1002</v>
+        <v>40</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>6</v>
@@ -6437,10 +6437,10 @@
         <v>1</v>
       </c>
       <c r="B431" s="2">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="C431" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>5</v>
@@ -6451,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="B432" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C432" s="2">
         <v>1</v>
@@ -6465,13 +6465,13 @@
         <v>1</v>
       </c>
       <c r="B433" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C433" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6479,10 +6479,10 @@
         <v>1</v>
       </c>
       <c r="B434" s="2">
-        <v>46003</v>
+        <v>45997</v>
       </c>
       <c r="C434" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>5</v>
@@ -6493,10 +6493,10 @@
         <v>1</v>
       </c>
       <c r="B435" s="2">
-        <v>46004</v>
+        <v>45997</v>
       </c>
       <c r="C435" s="2">
-        <v>5</v>
+        <v>1192</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>5</v>
@@ -6507,10 +6507,10 @@
         <v>1</v>
       </c>
       <c r="B436" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C436" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>5</v>
@@ -6521,13 +6521,13 @@
         <v>1</v>
       </c>
       <c r="B437" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C437" s="2">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6535,10 +6535,10 @@
         <v>1</v>
       </c>
       <c r="B438" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C438" s="2">
-        <v>3</v>
+        <v>570</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>5</v>
@@ -6549,13 +6549,13 @@
         <v>1</v>
       </c>
       <c r="B439" s="2">
-        <v>46005</v>
+        <v>46001</v>
       </c>
       <c r="C439" s="2">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6563,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="B440" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C440" s="2">
-        <v>6</v>
+        <v>997</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>5</v>
@@ -6577,13 +6577,13 @@
         <v>1</v>
       </c>
       <c r="B441" s="2">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="C441" s="2">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6591,13 +6591,13 @@
         <v>1</v>
       </c>
       <c r="B442" s="2">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C442" s="2">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="B443" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C443" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>5</v>
@@ -6622,10 +6622,10 @@
         <v>46010</v>
       </c>
       <c r="C444" s="2">
-        <v>109</v>
+        <v>243</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6636,7 +6636,7 @@
         <v>46011</v>
       </c>
       <c r="C445" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>5</v>
@@ -6647,10 +6647,10 @@
         <v>1</v>
       </c>
       <c r="B446" s="2">
-        <v>46011</v>
+        <v>46013</v>
       </c>
       <c r="C446" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>5</v>
@@ -6661,10 +6661,10 @@
         <v>1</v>
       </c>
       <c r="B447" s="2">
-        <v>46011</v>
+        <v>46013</v>
       </c>
       <c r="C447" s="2">
-        <v>350</v>
+        <v>447</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>8</v>
@@ -6675,10 +6675,10 @@
         <v>1</v>
       </c>
       <c r="B448" s="2">
-        <v>46012</v>
+        <v>46015</v>
       </c>
       <c r="C448" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>5</v>
@@ -6689,10 +6689,10 @@
         <v>1</v>
       </c>
       <c r="B449" s="2">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C449" s="2">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>5</v>
@@ -6703,13 +6703,13 @@
         <v>1</v>
       </c>
       <c r="B450" s="2">
-        <v>46014</v>
+        <v>46016</v>
       </c>
       <c r="C450" s="2">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6717,13 +6717,13 @@
         <v>1</v>
       </c>
       <c r="B451" s="2">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="C451" s="2">
-        <v>693</v>
+        <v>1</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6731,13 +6731,13 @@
         <v>1</v>
       </c>
       <c r="B452" s="2">
-        <v>46018</v>
+        <v>46016</v>
       </c>
       <c r="C452" s="2">
-        <v>12</v>
+        <v>1128</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6748,7 +6748,7 @@
         <v>46018</v>
       </c>
       <c r="C453" s="2">
-        <v>392</v>
+        <v>19</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>5</v>
@@ -6759,13 +6759,13 @@
         <v>1</v>
       </c>
       <c r="B454" s="2">
-        <v>46020</v>
+        <v>46019</v>
       </c>
       <c r="C454" s="2">
-        <v>12</v>
+        <v>1242</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6773,13 +6773,13 @@
         <v>1</v>
       </c>
       <c r="B455" s="2">
-        <v>46021</v>
+        <v>46019</v>
       </c>
       <c r="C455" s="2">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6787,10 +6787,10 @@
         <v>1</v>
       </c>
       <c r="B456" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C456" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>5</v>
@@ -6804,7 +6804,7 @@
         <v>46021</v>
       </c>
       <c r="C457" s="2">
-        <v>460</v>
+        <v>53</v>
       </c>
       <c r="D457" s="2" t="s">
         <v>5</v>
@@ -6815,10 +6815,10 @@
         <v>1</v>
       </c>
       <c r="B458" s="2">
-        <v>46023</v>
+        <v>46021</v>
       </c>
       <c r="C458" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>5</v>
@@ -6829,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="B459" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="C459" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D459" s="2" t="s">
         <v>5</v>
@@ -6843,13 +6843,13 @@
         <v>1</v>
       </c>
       <c r="B460" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="C460" s="2">
-        <v>987</v>
+        <v>1290</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6857,10 +6857,10 @@
         <v>1</v>
       </c>
       <c r="B461" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="C461" s="2">
-        <v>1622</v>
+        <v>482</v>
       </c>
       <c r="D461" s="2" t="s">
         <v>6</v>
@@ -6871,10 +6871,10 @@
         <v>1</v>
       </c>
       <c r="B462" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C462" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D462" s="2" t="s">
         <v>5</v>
@@ -6888,7 +6888,7 @@
         <v>46025</v>
       </c>
       <c r="C463" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>5</v>
@@ -6902,10 +6902,10 @@
         <v>46025</v>
       </c>
       <c r="C464" s="2">
-        <v>566</v>
+        <v>2</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6913,13 +6913,13 @@
         <v>1</v>
       </c>
       <c r="B465" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C465" s="2">
-        <v>3</v>
+        <v>551</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6927,10 +6927,10 @@
         <v>1</v>
       </c>
       <c r="B466" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C466" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
         <v>5</v>
@@ -6941,10 +6941,10 @@
         <v>1</v>
       </c>
       <c r="B467" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C467" s="2">
-        <v>550</v>
+        <v>658</v>
       </c>
       <c r="D467" s="2" t="s">
         <v>5</v>
@@ -6955,13 +6955,13 @@
         <v>1</v>
       </c>
       <c r="B468" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C468" s="2">
-        <v>1826</v>
+        <v>3</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6972,10 +6972,10 @@
         <v>46028</v>
       </c>
       <c r="C469" s="2">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
